--- a/sample_data/Sample_GSTR_2B.xlsx
+++ b/sample_data/Sample_GSTR_2B.xlsx
@@ -14,11 +14,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="40">
   <si>
     <t>GSTIN</t>
   </si>
   <si>
+    <t>Supplier Name</t>
+  </si>
+  <si>
     <t>Invoice No</t>
   </si>
   <si>
@@ -40,19 +43,34 @@
     <t>SGST</t>
   </si>
   <si>
+    <t>Invoice Value</t>
+  </si>
+  <si>
     <t>Cess</t>
   </si>
   <si>
-    <t>Invoice Value</t>
-  </si>
-  <si>
-    <t>29ABCDE1234F1Z5</t>
-  </si>
-  <si>
-    <t>27PQRSX5678L1Z2</t>
-  </si>
-  <si>
-    <t>07LMNOP6789A1Z9</t>
+    <t>29ABCDE1234F1ZW</t>
+  </si>
+  <si>
+    <t>27PQRSX5678L1ZW</t>
+  </si>
+  <si>
+    <t>07LMNOP6789A1ZB</t>
+  </si>
+  <si>
+    <t>27KLMNO4321Q1ZB</t>
+  </si>
+  <si>
+    <t>Sunrise Trading Company Pvt Ltd</t>
+  </si>
+  <si>
+    <t>Meridian Steels LLP</t>
+  </si>
+  <si>
+    <t>Nova Electricals Private Limited</t>
+  </si>
+  <si>
+    <t>Orbit Chemicals Ltd</t>
   </si>
   <si>
     <t>INV-1001</t>
@@ -70,38 +88,60 @@
     <t>INV-1005</t>
   </si>
   <si>
-    <t>01-12-2025</t>
-  </si>
-  <si>
-    <t>05-12-2025</t>
-  </si>
-  <si>
-    <t>08-12-2025</t>
-  </si>
-  <si>
-    <t>10-12-2025</t>
-  </si>
-  <si>
-    <t>12-12-2025</t>
-  </si>
-  <si>
-    <t>Dec-25</t>
+    <t>INV/1006/26-27</t>
+  </si>
+  <si>
+    <t>INV-1007</t>
+  </si>
+  <si>
+    <t>INV-1008</t>
+  </si>
+  <si>
+    <t>INV-1009</t>
+  </si>
+  <si>
+    <t>OC-2001</t>
+  </si>
+  <si>
+    <t>01-06-2026</t>
+  </si>
+  <si>
+    <t>05-06-2026</t>
+  </si>
+  <si>
+    <t>08-06-2026</t>
+  </si>
+  <si>
+    <t>10-06-2026</t>
+  </si>
+  <si>
+    <t>12-06-2026</t>
+  </si>
+  <si>
+    <t>14-06-2026</t>
+  </si>
+  <si>
+    <t>16-06-2026</t>
+  </si>
+  <si>
+    <t>18-06-2026</t>
+  </si>
+  <si>
+    <t>20-06-2026</t>
+  </si>
+  <si>
+    <t>22-06-2026</t>
+  </si>
+  <si>
+    <t>Jun-26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -117,7 +157,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -125,30 +165,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -443,62 +465,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2">
         <v>10000</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>1800</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -509,28 +534,31 @@
       <c r="J2">
         <v>11800</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3">
         <v>20000</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>3600</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -541,60 +569,66 @@
       <c r="J3">
         <v>23600</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4">
         <v>15000</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>1350</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>1350</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1350</v>
       </c>
       <c r="J4">
         <v>17700</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5">
         <v>5000</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>900</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -605,28 +639,31 @@
       <c r="J5">
         <v>5900</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6">
         <v>8000</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>1440</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -636,6 +673,184 @@
       </c>
       <c r="J6">
         <v>9440</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7">
+        <v>12000</v>
+      </c>
+      <c r="G7">
+        <v>2160</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>14160</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8">
+        <v>10000</v>
+      </c>
+      <c r="G8">
+        <v>1800</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>11800</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9">
+        <v>4000</v>
+      </c>
+      <c r="G9">
+        <v>720</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>4720</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10">
+        <v>20000</v>
+      </c>
+      <c r="G10">
+        <v>3600</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>23600</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11">
+        <v>50000</v>
+      </c>
+      <c r="G11">
+        <v>9000</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>59000</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data/Sample_GSTR_2B.xlsx
+++ b/sample_data/Sample_GSTR_2B.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="45">
   <si>
     <t>GSTIN</t>
   </si>
@@ -43,12 +43,12 @@
     <t>SGST</t>
   </si>
   <si>
+    <t>Cess</t>
+  </si>
+  <si>
     <t>Invoice Value</t>
   </si>
   <si>
-    <t>Cess</t>
-  </si>
-  <si>
     <t>29ABCDE1234F1ZW</t>
   </si>
   <si>
@@ -103,6 +103,12 @@
     <t>OC-2001</t>
   </si>
   <si>
+    <t>INV-1010</t>
+  </si>
+  <si>
+    <t>MISC-01</t>
+  </si>
+  <si>
     <t>01-06-2026</t>
   </si>
   <si>
@@ -133,7 +139,16 @@
     <t>22-06-2026</t>
   </si>
   <si>
+    <t>24-06-2026</t>
+  </si>
+  <si>
+    <t>26-06-2026</t>
+  </si>
+  <si>
     <t>Jun-26</t>
+  </si>
+  <si>
+    <t>Jul-26</t>
   </si>
 </sst>
 </file>
@@ -465,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -514,10 +529,10 @@
         <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F2">
         <v>10000</v>
@@ -532,10 +547,10 @@
         <v>0</v>
       </c>
       <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
         <v>11800</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -549,10 +564,10 @@
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F3">
         <v>20000</v>
@@ -567,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
         <v>23600</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -584,10 +599,10 @@
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F4">
         <v>15000</v>
@@ -602,10 +617,10 @@
         <v>1350</v>
       </c>
       <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>17700</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -619,10 +634,10 @@
         <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F5">
         <v>5000</v>
@@ -637,10 +652,10 @@
         <v>0</v>
       </c>
       <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
         <v>5900</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -654,10 +669,10 @@
         <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F6">
         <v>8000</v>
@@ -672,10 +687,10 @@
         <v>0</v>
       </c>
       <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>9440</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -689,10 +704,10 @@
         <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F7">
         <v>12000</v>
@@ -707,10 +722,10 @@
         <v>0</v>
       </c>
       <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>14160</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -724,10 +739,10 @@
         <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F8">
         <v>10000</v>
@@ -742,10 +757,10 @@
         <v>0</v>
       </c>
       <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>11800</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -759,10 +774,10 @@
         <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F9">
         <v>4000</v>
@@ -777,10 +792,10 @@
         <v>0</v>
       </c>
       <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
         <v>4720</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -794,10 +809,10 @@
         <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F10">
         <v>20000</v>
@@ -812,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
         <v>23600</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -829,10 +844,10 @@
         <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F11">
         <v>50000</v>
@@ -847,10 +862,80 @@
         <v>0</v>
       </c>
       <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>59000</v>
       </c>
-      <c r="K11">
-        <v>0</v>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12">
+        <v>30000</v>
+      </c>
+      <c r="G12">
+        <v>5400</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>35400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13">
+        <v>6000</v>
+      </c>
+      <c r="G13">
+        <v>1080</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>7080</v>
       </c>
     </row>
   </sheetData>
